--- a/Tools/_test_corpus/fixtures/pv-338338.xlsx
+++ b/Tools/_test_corpus/fixtures/pv-338338.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\source\repos\RapidReconciler-AI\.claude\worktrees\recursing-williamson-0f6630\Tools\_test_corpus\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49B9742E-469C-47A3-99FB-2553E11ABE92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A034029A-CA74-467B-9C61-5C49EDF8C9C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="720" windowWidth="22275" windowHeight="14640" xr2:uid="{C8C3070D-7E66-40B9-9BE6-B89A712159CD}"/>
+    <workbookView xWindow="2220" yWindow="720" windowWidth="22275" windowHeight="14640" xr2:uid="{A3F2E3EC-F3CC-4133-8E21-8668EE6D05C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Transaction Details" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="141">
   <si>
-    <t>Transaction Details Generated Monday, May 18, 2026 05:53 PM</t>
+    <t>Transaction Details Generated Monday, May 18, 2026 11:01 PM</t>
   </si>
   <si>
     <t>Period</t>
@@ -842,7 +842,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{911767F5-EE85-4DCB-98F7-C4AE26B8FE71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55231D0D-134A-46A2-AC31-806406607BE6}">
   <dimension ref="A1:AB48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
